--- a/backend/static_assets/SPOT_JobType_Variance_v3.xlsx
+++ b/backend/static_assets/SPOT_JobType_Variance_v3.xlsx
@@ -35923,7 +35923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35968,23 +35968,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>223583</v>
+        <v>223878</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J63068 - Moen Lowes Prepacks (Project 7655)</t>
+          <t>Walmart Sidekick Display - Lubrication Specialties (Hot Shot's Secret)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iQuote '222300' qty=919 — same-name SPOT row priced at different qty</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>222300</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>6590.63</v>
+          <t>SPOT 'Walmart Sidekick Shelf (4-up digitally printed sheets, Skybox to die cut)' qty=1000 — same-name iQuote row priced at different qty</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>2672.89</v>
       </c>
     </row>
     <row r="3">
@@ -35998,11 +35995,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SPOT 'Walmart Sidekick Shelf (4-up digitally printed sheets, Skybox to die cut)' qty=1000 — same-name iQuote row priced at different qty</t>
+          <t>SPOT 'Header - digitally printed and CAD cut' qty=500 — same-name iQuote row priced at different qty</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>2672.89</v>
+        <v>1109.9</v>
       </c>
     </row>
     <row r="4">
@@ -36016,11 +36013,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SPOT 'Header - digitally printed and CAD cut' qty=500 — same-name iQuote row priced at different qty</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1109.9</v>
+          <t>iQuote 'Shelf' qty=500 — same-name SPOT row priced at different qty</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shelf</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1979.54</v>
       </c>
     </row>
     <row r="5">
@@ -36034,39 +36036,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>iQuote 'Shelf' qty=500 — same-name SPOT row priced at different qty</t>
+          <t>iQuote 'Header' qty=1000 — same-name SPOT row priced at different qty</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shelf</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1979.54</v>
+        <v>820.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>223878</v>
+        <v>224377</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Walmart Sidekick Display - Lubrication Specialties (Hot Shot's Secret)</t>
+          <t>44000 90245 2027 Oreo IMC Large DBL Kit — Digital Innovation Hutch Kit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>iQuote 'Header' qty=1000 — same-name SPOT row priced at different qty</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>820.61</v>
+          <t>SPOT '12ct. HSC Bin' qty=400 — same-name iQuote row priced at different qty</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5625.11</v>
       </c>
     </row>
     <row r="7">
@@ -36080,11 +36077,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SPOT '12ct. HSC Bin' qty=400 — same-name iQuote row priced at different qty</t>
+          <t>SPOT 'Inner Shelves' qty=400 — same-name iQuote row priced at different qty</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5625.11</v>
+        <v>16565.7</v>
       </c>
     </row>
     <row r="8">
@@ -36098,11 +36095,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SPOT 'Inner Shelves' qty=400 — same-name iQuote row priced at different qty</t>
+          <t>SPOT 'Motion Cookie Header' qty=800 — same-name iQuote row priced at different qty</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>16565.7</v>
+        <v>6937.09</v>
       </c>
     </row>
     <row r="9">
@@ -36116,11 +36113,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SPOT 'Motion Cookie Header' qty=800 — same-name iQuote row priced at different qty</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>6937.09</v>
+          <t>iQuote 'Shelves' qty=800 — same-name SPOT row priced at different qty</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shelves</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>12036.09</v>
       </c>
     </row>
     <row r="10">
@@ -36134,38 +36136,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iQuote 'Shelves' qty=800 — same-name SPOT row priced at different qty</t>
+          <t>iQuote 'Cookie Header' qty=400 — same-name SPOT row priced at different qty</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shelves</t>
+          <t>Cookie Header</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>12036.09</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>224377</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>44000 90245 2027 Oreo IMC Large DBL Kit — Digital Innovation Hutch Kit</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>iQuote 'Cookie Header' qty=400 — same-name SPOT row priced at different qty</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Cookie Header</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
         <v>6144.66</v>
       </c>
     </row>
@@ -36544,7 +36523,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>UNMATCHED (see 'Unmatched' tab): 10</t>
+          <t>UNMATCHED (see 'Unmatched' tab): 9</t>
         </is>
       </c>
     </row>
